--- a/results/04-2026/04.30 no_obbba/beta/contributions-04-2026.xlsx
+++ b/results/04-2026/04.30 no_obbba/beta/contributions-04-2026.xlsx
@@ -829,22 +829,22 @@
         <v>0.218260041490563</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.74486573546583</v>
+        <v>8.6385202038646</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.9309395294461</v>
+        <v>8.82499612592057</v>
       </c>
       <c r="AD3" t="n">
         <v>0.218260041490563</v>
       </c>
       <c r="AE3" t="n">
-        <v>8.62039918521447</v>
+        <v>8.51405365361324</v>
       </c>
       <c r="AF3" t="n">
-        <v>10.3706481717992</v>
+        <v>10.2647047682737</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.00961320689186</v>
+        <v>2.98312735601048</v>
       </c>
     </row>
     <row r="4">
@@ -930,22 +930,22 @@
         <v>0.552346472186169</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.16139327319511</v>
+        <v>4.96965012385782</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.69127333718764</v>
+        <v>5.50037041244838</v>
       </c>
       <c r="AD4" t="n">
         <v>0.552346472186169</v>
       </c>
       <c r="AE4" t="n">
-        <v>4.96184053113914</v>
+        <v>4.77009738180184</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.99126378849784</v>
+        <v>3.80036086375858</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.83799587371516</v>
+        <v>3.76378429164896</v>
       </c>
     </row>
     <row r="5">
@@ -1031,22 +1031,22 @@
         <v>-0.568772712361355</v>
       </c>
       <c r="AB5" t="n">
-        <v>-2.35235872955152</v>
+        <v>-2.49294901262296</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.93502940425967</v>
+        <v>-3.07644678264991</v>
       </c>
       <c r="AD5" t="n">
         <v>-0.568772712361355</v>
       </c>
       <c r="AE5" t="n">
-        <v>-2.48939682148616</v>
+        <v>-2.6299871045576</v>
       </c>
       <c r="AF5" t="n">
-        <v>-3.200759544567</v>
+        <v>-3.34217692295723</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.90763406238303</v>
+        <v>2.79806813571927</v>
       </c>
     </row>
     <row r="6">
@@ -1132,22 +1132,22 @@
         <v>-0.193345941150108</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.93378769759511</v>
+        <v>7.81623210851637</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.75569645454409</v>
+        <v>7.63791171392507</v>
       </c>
       <c r="AD6" t="n">
         <v>-0.193345941150108</v>
       </c>
       <c r="AE6" t="n">
-        <v>7.80632121184456</v>
+        <v>7.68876562276582</v>
       </c>
       <c r="AF6" t="n">
-        <v>8.53446341474537</v>
+        <v>8.41667867412635</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.92390395761885</v>
+        <v>4.78489184580034</v>
       </c>
     </row>
     <row r="7">
@@ -1233,22 +1233,22 @@
         <v>-0.24689103402653</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1.00963271046716</v>
+        <v>-1.08052926851467</v>
       </c>
       <c r="AC7" t="n">
-        <v>-1.25880069434664</v>
+        <v>-1.32985687880309</v>
       </c>
       <c r="AD7" t="n">
         <v>-0.24689103402653</v>
       </c>
       <c r="AE7" t="n">
-        <v>-1.07983609284451</v>
+        <v>-1.15073265089202</v>
       </c>
       <c r="AF7" t="n">
-        <v>-2.46938623188051</v>
+        <v>-2.54044241633695</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.71389535669892</v>
+        <v>1.58360504964769</v>
       </c>
     </row>
     <row r="8">
@@ -1334,22 +1334,22 @@
         <v>-0.31515314337929</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.06113735720888</v>
+        <v>-2.09082065057731</v>
       </c>
       <c r="AC8" t="n">
-        <v>-2.38279100305357</v>
+        <v>-2.41256759108425</v>
       </c>
       <c r="AD8" t="n">
         <v>-0.31515314337929</v>
       </c>
       <c r="AE8" t="n">
-        <v>-2.09021198351942</v>
+        <v>-2.11989527688785</v>
       </c>
       <c r="AF8" t="n">
-        <v>-3.28834949142401</v>
+        <v>-3.31812607945469</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.106007963281536</v>
+        <v>-0.196016686155632</v>
       </c>
     </row>
     <row r="9">
@@ -1435,22 +1435,22 @@
         <v>-0.208789857580898</v>
       </c>
       <c r="AB9" t="n">
-        <v>-2.42092105160786</v>
+        <v>-2.44734167709947</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.63468816179706</v>
+        <v>-2.66116289194415</v>
       </c>
       <c r="AD9" t="n">
         <v>-0.208789857580898</v>
       </c>
       <c r="AE9" t="n">
-        <v>-2.44671974554818</v>
+        <v>-2.47314037103979</v>
       </c>
       <c r="AF9" t="n">
-        <v>-3.03402546115842</v>
+        <v>-3.0605001913055</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.0643244424293917</v>
+        <v>-0.1255975032427</v>
       </c>
     </row>
     <row r="10">
@@ -1536,22 +1536,22 @@
         <v>-0.876075859460641</v>
       </c>
       <c r="AB10" t="n">
-        <v>-2.16798383433384</v>
+        <v>-2.18260935157057</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.06339026497288</v>
+        <v>-3.07814571216895</v>
       </c>
       <c r="AD10" t="n">
         <v>-0.876075859460641</v>
       </c>
       <c r="AE10" t="n">
-        <v>-2.18229105712882</v>
+        <v>-2.19691657436556</v>
       </c>
       <c r="AF10" t="n">
-        <v>-3.9851923303055</v>
+        <v>-3.99994777750156</v>
       </c>
       <c r="AG10" t="n">
-        <v>-3.19423837869211</v>
+        <v>-3.22975411614968</v>
       </c>
     </row>
     <row r="11">
@@ -1637,22 +1637,22 @@
         <v>-1.20568398792863</v>
       </c>
       <c r="AB11" t="n">
-        <v>-3.11959610857322</v>
+        <v>-3.10202058067492</v>
       </c>
       <c r="AC11" t="n">
-        <v>-4.36239862308495</v>
+        <v>-4.34461502100846</v>
       </c>
       <c r="AD11" t="n">
         <v>-1.20568398792863</v>
       </c>
       <c r="AE11" t="n">
-        <v>-3.10254365284433</v>
+        <v>-3.08496812494604</v>
       </c>
       <c r="AF11" t="n">
-        <v>-5.03050054385313</v>
+        <v>-5.01271694177664</v>
       </c>
       <c r="AG11" t="n">
-        <v>-3.83451695668526</v>
+        <v>-3.8478227475096</v>
       </c>
     </row>
     <row r="12">
@@ -1738,22 +1738,22 @@
         <v>-0.580579627213782</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.72627805103759</v>
+        <v>-1.71429964147729</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.31716754988747</v>
+        <v>-2.30511780955395</v>
       </c>
       <c r="AD12" t="n">
         <v>-0.657494577538429</v>
       </c>
       <c r="AE12" t="n">
-        <v>-1.71450742085577</v>
+        <v>-1.70252901129547</v>
       </c>
       <c r="AF12" t="n">
-        <v>-2.4535369856565</v>
+        <v>-2.44148724532298</v>
       </c>
       <c r="AG12" t="n">
-        <v>-3.62581383024339</v>
+        <v>-3.62866303897667</v>
       </c>
     </row>
     <row r="13">
@@ -1839,22 +1839,22 @@
         <v>-0.282595033045533</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.45442319460995</v>
+        <v>-0.443693965838321</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.73836697138364</v>
+        <v>-0.727605922570038</v>
       </c>
       <c r="AD13" t="n">
         <v>-0.332348599335242</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.443743756909895</v>
+        <v>-0.433014528138266</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.4617576379428</v>
+        <v>-0.450996589129198</v>
       </c>
       <c r="AG13" t="n">
-        <v>-2.98274687443948</v>
+        <v>-2.9762871384326</v>
       </c>
     </row>
     <row r="14">
@@ -1940,22 +1940,22 @@
         <v>0.818846407620433</v>
       </c>
       <c r="AB14" t="n">
-        <v>-1.25281556342879</v>
+        <v>-1.24218523157011</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.423500585246295</v>
+        <v>-0.412958895759776</v>
       </c>
       <c r="AD14" t="n">
         <v>0.46615754920793</v>
       </c>
       <c r="AE14" t="n">
-        <v>-1.24231811101493</v>
+        <v>-1.23168777915626</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.163281667950414</v>
+        <v>-0.152739978463895</v>
       </c>
       <c r="AG14" t="n">
-        <v>-2.02726920885071</v>
+        <v>-2.01448518867318</v>
       </c>
     </row>
     <row r="15">
@@ -2041,22 +2041,22 @@
         <v>0.762928566953573</v>
       </c>
       <c r="AB15" t="n">
-        <v>-1.39123103603504</v>
+        <v>-1.38234978467433</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.617103421087763</v>
+        <v>-0.608293490344936</v>
       </c>
       <c r="AD15" t="n">
         <v>0.528053936044742</v>
       </c>
       <c r="AE15" t="n">
-        <v>-1.38247728801657</v>
+        <v>-1.37359603665586</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.508833279663284</v>
+        <v>-0.500023348920457</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.89685239280325</v>
+        <v>-0.886311790459134</v>
       </c>
     </row>
     <row r="16">
@@ -2142,22 +2142,22 @@
         <v>0.412030542300483</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.796177903897253</v>
+        <v>-0.656622075925647</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.380727188578476</v>
+        <v>-0.241770177412637</v>
       </c>
       <c r="AD16" t="n">
         <v>0.18171700258577</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.657570272399199</v>
+        <v>-0.518014444427592</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.047554997712165</v>
+        <v>0.186512008878004</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.271579396961083</v>
+        <v>-0.229311976908887</v>
       </c>
     </row>
     <row r="17">
@@ -2243,22 +2243,22 @@
         <v>0.168106654503534</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.776344234660777</v>
+        <v>-0.662422579376793</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.60685770938353</v>
+        <v>-0.493138303132385</v>
       </c>
       <c r="AD17" t="n">
         <v>0.0862390375637294</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.663214681106842</v>
+        <v>-0.549293025822858</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.268887888907778</v>
+        <v>-0.155168482656634</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.223361959702328</v>
+        <v>-0.155354950290746</v>
       </c>
     </row>
     <row r="18">
@@ -2344,22 +2344,22 @@
         <v>0.78628460647213</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.559877459260424</v>
+        <v>-0.454576284540892</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.231049610408206</v>
+        <v>0.335478327415625</v>
       </c>
       <c r="AD18" t="n">
         <v>0.659854636965577</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.455077977525216</v>
+        <v>-0.349776802805683</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.170010109447605</v>
+        <v>0.274438826455024</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.140039015352823</v>
+        <v>-0.0485602490610162</v>
       </c>
     </row>
     <row r="19">
@@ -2445,22 +2445,22 @@
         <v>0.602362580528956</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.48090178331643</v>
+        <v>-0.384207077760455</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.12447112969564</v>
+        <v>0.22056094924408</v>
       </c>
       <c r="AD19" t="n">
         <v>0.508714905565415</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.384591213069866</v>
+        <v>-0.287896507513891</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.245206407186424</v>
+        <v>0.341296226734864</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.048470906359604</v>
+        <v>0.161769644852814</v>
       </c>
     </row>
     <row r="20">
@@ -2546,22 +2546,22 @@
         <v>0.180384979214747</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.0742382360498926</v>
+        <v>-0.01888745513281</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.106286927910456</v>
+        <v>0.161533192877544</v>
       </c>
       <c r="AD20" t="n">
         <v>0.274816107829201</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.0188983933689314</v>
+        <v>0.0364523875481512</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.601612029340773</v>
+        <v>0.65685829430786</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.186985164266756</v>
+        <v>0.279356216210278</v>
       </c>
     </row>
     <row r="21">
@@ -2647,22 +2647,22 @@
         <v>0.168699850674615</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.203974334374208</v>
+        <v>0.234191950358427</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.37231700923784</v>
+        <v>0.40248169023671</v>
       </c>
       <c r="AD21" t="n">
         <v>0.303037201695179</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.234265563271938</v>
+        <v>0.264483179256157</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.511324456276486</v>
+        <v>0.541489137275356</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.382038250562822</v>
+        <v>0.453520621193276</v>
       </c>
     </row>
     <row r="22">
@@ -2748,22 +2748,22 @@
         <v>-0.0973949910447126</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.00437632570967921</v>
+        <v>0.0253809191774514</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.101775817864685</v>
+        <v>-0.0719879658795382</v>
       </c>
       <c r="AD22" t="n">
         <v>0.0179122702725422</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.0253888984688642</v>
+        <v>0.0551461433559948</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.695053673063814</v>
+        <v>-0.665265821078667</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.165772304934967</v>
+        <v>0.218594459309853</v>
       </c>
     </row>
     <row r="23">
@@ -2849,22 +2849,22 @@
         <v>-0.274529505412121</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.445899379286268</v>
+        <v>0.469120272922062</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.0273475251368821</v>
+        <v>-0.00405978308432048</v>
       </c>
       <c r="AD23" t="n">
         <v>-0.491452879857937</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.469235029434092</v>
+        <v>0.492455923069887</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.4331894038576</v>
+        <v>-0.409901661805038</v>
       </c>
       <c r="AG23" t="n">
-        <v>-0.00382664782603897</v>
+        <v>0.0307949871748775</v>
       </c>
     </row>
     <row r="24">
@@ -2950,22 +2950,22 @@
         <v>-0.468394735010296</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.400839231761259</v>
+        <v>0.430461654873164</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.065613739105092</v>
+        <v>-0.0358477105708311</v>
       </c>
       <c r="AD24" t="n">
         <v>-0.702326657449005</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.43059422877991</v>
+        <v>0.460216651891816</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0.320709449888415</v>
+        <v>-0.290943421354154</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0.234407017633336</v>
+        <v>-0.206155441740626</v>
       </c>
     </row>
     <row r="25">
@@ -3051,22 +3051,22 @@
         <v>-0.468782871390628</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.350744325797961</v>
+        <v>0.374913037337643</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.116306636435559</v>
+        <v>-0.0920185053895342</v>
       </c>
       <c r="AD25" t="n">
         <v>-0.61126600917892</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.375008938275619</v>
+        <v>0.399177649815301</v>
       </c>
       <c r="AF25" t="n">
-        <v>-1.54126750425894</v>
+        <v>-1.51697937321292</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.747555007767193</v>
+        <v>-0.720772569362695</v>
       </c>
     </row>
     <row r="26">
@@ -3152,22 +3152,22 @@
         <v>-0.0580644896503875</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.0607909371826069</v>
+        <v>-0.0595372444908254</v>
       </c>
       <c r="AC26" t="n">
-        <v>-0.0588921077009862</v>
+        <v>-0.0576376586169369</v>
       </c>
       <c r="AD26" t="n">
         <v>-0.372580266741774</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.0595380197466163</v>
+        <v>-0.0582843270548348</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.0987477241290138</v>
+        <v>0.100002173213063</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.549104658468986</v>
+        <v>-0.529455570789762</v>
       </c>
     </row>
     <row r="27">
@@ -3253,22 +3253,22 @@
         <v>-0.0192998238186113</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.0153552269839062</v>
+        <v>-0.0122711727831255</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.0253418426160484</v>
+        <v>0.0284265207516185</v>
       </c>
       <c r="AD27" t="n">
         <v>-0.270843463749101</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.0122715694629087</v>
+        <v>-0.00918751526212806</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.513625992353055</v>
+        <v>-0.510541314217485</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.56921380559285</v>
+        <v>-0.554615483892874</v>
       </c>
     </row>
     <row r="28">
@@ -3354,22 +3354,22 @@
         <v>-0.0332280122662193</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.0791647305176549</v>
+        <v>0.0749074503856171</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.105964407859203</v>
+        <v>0.101705638453785</v>
       </c>
       <c r="AD28" t="n">
         <v>-0.111158622235428</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.0749040906442924</v>
+        <v>0.0706468105122546</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.281300803192296</v>
+        <v>-0.285559572597715</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.55936164391882</v>
+        <v>-0.553269521703764</v>
       </c>
     </row>
     <row r="29">
@@ -3455,22 +3455,22 @@
         <v>-0.342455494736299</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.152921530322002</v>
+        <v>0.14430313612956</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.128981075696634</v>
+        <v>-0.137630637681231</v>
       </c>
       <c r="AD29" t="n">
         <v>-0.290163880535587</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.144289978101072</v>
+        <v>0.13567158390863</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.43037560709953</v>
+        <v>-0.439025169084127</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.281638669628967</v>
+        <v>-0.283780970671566</v>
       </c>
     </row>
     <row r="30">
@@ -3556,22 +3556,22 @@
         <v>-0.950363578625895</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.252284646513646</v>
+        <v>0.249916716336935</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.635540979788829</v>
+        <v>-0.63793274162743</v>
       </c>
       <c r="AD30" t="n">
         <v>-0.683489631104003</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.249910424979606</v>
+        <v>0.247542494802894</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.928107122922732</v>
+        <v>-0.930498884761333</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.538352381391903</v>
+        <v>-0.541406235165165</v>
       </c>
     </row>
     <row r="31">
@@ -3657,22 +3657,22 @@
         <v>-0.891228157837452</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.127712217073583</v>
+        <v>0.128035630697752</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.702308510116384</v>
+        <v>-0.701982038143995</v>
       </c>
       <c r="AD31" t="n">
         <v>-0.527405741537913</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.128036071255768</v>
+        <v>0.128359484879937</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.973821354133907</v>
+        <v>-0.973494882161518</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.653401221837116</v>
+        <v>-0.657144627151173</v>
       </c>
     </row>
     <row r="32">
@@ -3758,22 +3758,22 @@
         <v>-0.505561622018449</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.0714902053480665</v>
+        <v>0.0664563734820875</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.433688099565149</v>
+        <v>-0.438748925076625</v>
       </c>
       <c r="AD32" t="n">
         <v>-0.119132346638716</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.0664528198971211</v>
+        <v>0.0614189880311421</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.718780319451678</v>
+        <v>-0.723841144963155</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.762771100901962</v>
+        <v>-0.766715020242533</v>
       </c>
     </row>
     <row r="33">
@@ -3859,22 +3859,22 @@
         <v>-0.48701151625661</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.0396906243345246</v>
+        <v>0.0357511751123616</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.447115649814463</v>
+        <v>-0.451075471408537</v>
       </c>
       <c r="AD33" t="n">
         <v>-0.0582945542300506</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.0357496778297344</v>
+        <v>0.0318102286075714</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.796464349806649</v>
+        <v>-0.800424171400723</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.854293286578741</v>
+        <v>-0.857064770821682</v>
       </c>
     </row>
     <row r="34">
@@ -3975,7 +3975,7 @@
         <v>-1.06593231454812</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.888749584485089</v>
+        <v>-0.890923128268379</v>
       </c>
     </row>
   </sheetData>
